--- a/vch1101/files/kahoot/VCH1101_Kahoot_Unit4.xlsx
+++ b/vch1101/files/kahoot/VCH1101_Kahoot_Unit4.xlsx
@@ -717,17 +717,17 @@
       </c>
       <c r="D9" s="22" t="inlineStr">
         <is>
+          <t>Post-it</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>口頭講</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
           <t>WhatsApp逐張相咁send</t>
-        </is>
-      </c>
-      <c r="E9" s="22" t="inlineStr">
-        <is>
-          <t>口頭講</t>
-        </is>
-      </c>
-      <c r="F9" s="22" t="inlineStr">
-        <is>
-          <t>Post-it</t>
         </is>
       </c>
       <c r="G9" s="22" t="n">
@@ -751,22 +751,22 @@
       </c>
       <c r="C10" s="25" t="inlineStr">
         <is>
+          <t>只需知悉唔使執行</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>標題要簡明扼要</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t>受文者電郵地址</t>
+        </is>
+      </c>
+      <c r="F10" s="25" t="inlineStr">
+        <is>
           <t>暗中通知嘅受文人</t>
-        </is>
-      </c>
-      <c r="D10" s="25" t="inlineStr">
-        <is>
-          <t>標題要簡明扼要</t>
-        </is>
-      </c>
-      <c r="E10" s="25" t="inlineStr">
-        <is>
-          <t>只需知悉唔使執行</t>
-        </is>
-      </c>
-      <c r="F10" s="25" t="inlineStr">
-        <is>
-          <t>受文者電郵地址</t>
         </is>
       </c>
       <c r="G10" s="25" t="n">
@@ -774,7 +774,7 @@
       </c>
       <c r="H10" s="26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I10" s="1" t="n"/>
@@ -790,22 +790,22 @@
       </c>
       <c r="C11" s="25" t="inlineStr">
         <is>
+          <t>數量不足</t>
+        </is>
+      </c>
+      <c r="D11" s="25" t="inlineStr">
+        <is>
+          <t>送貨太慢</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>品質低劣</t>
+        </is>
+      </c>
+      <c r="F11" s="25" t="inlineStr">
+        <is>
           <t>顏色錯誤：訂淺藍色，收到粉紅色</t>
-        </is>
-      </c>
-      <c r="D11" s="25" t="inlineStr">
-        <is>
-          <t>數量不足</t>
-        </is>
-      </c>
-      <c r="E11" s="25" t="inlineStr">
-        <is>
-          <t>品質低劣</t>
-        </is>
-      </c>
-      <c r="F11" s="25" t="inlineStr">
-        <is>
-          <t>送貨太慢</t>
         </is>
       </c>
       <c r="G11" s="25" t="n">
@@ -813,7 +813,7 @@
       </c>
       <c r="H11" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I11" s="1" t="n"/>
@@ -829,12 +829,12 @@
       </c>
       <c r="C12" s="25" t="inlineStr">
         <is>
+          <t>號</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
           <t>篇</t>
-        </is>
-      </c>
-      <c r="D12" s="25" t="inlineStr">
-        <is>
-          <t>號</t>
         </is>
       </c>
       <c r="E12" s="25" t="inlineStr"/>
@@ -844,7 +844,7 @@
       </c>
       <c r="H12" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" s="1" t="n"/>
@@ -860,22 +860,22 @@
       </c>
       <c r="C13" s="25" t="inlineStr">
         <is>
+          <t>查下</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="inlineStr">
+        <is>
+          <t>審查</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t>睇睇</t>
+        </is>
+      </c>
+      <c r="F13" s="25" t="inlineStr">
+        <is>
           <t>調查</t>
-        </is>
-      </c>
-      <c r="D13" s="25" t="inlineStr">
-        <is>
-          <t>審查</t>
-        </is>
-      </c>
-      <c r="E13" s="25" t="inlineStr">
-        <is>
-          <t>睇睇</t>
-        </is>
-      </c>
-      <c r="F13" s="25" t="inlineStr">
-        <is>
-          <t>查下</t>
         </is>
       </c>
       <c r="G13" s="25" t="n">
@@ -883,7 +883,7 @@
       </c>
       <c r="H13" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I13" s="1" t="n"/>
@@ -899,22 +899,22 @@
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
+          <t>5天</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>3天：6月9至11日</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="inlineStr">
+        <is>
+          <t>1天</t>
+        </is>
+      </c>
+      <c r="F14" s="25" t="inlineStr">
+        <is>
           <t>2天：6月10日及11日</t>
-        </is>
-      </c>
-      <c r="D14" s="25" t="inlineStr">
-        <is>
-          <t>3天：6月9至11日</t>
-        </is>
-      </c>
-      <c r="E14" s="25" t="inlineStr">
-        <is>
-          <t>1天</t>
-        </is>
-      </c>
-      <c r="F14" s="25" t="inlineStr">
-        <is>
-          <t>5天</t>
         </is>
       </c>
       <c r="G14" s="25" t="n">
@@ -922,7 +922,7 @@
       </c>
       <c r="H14" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I14" s="1" t="n"/>
@@ -938,17 +938,17 @@
       </c>
       <c r="C15" s="25" t="inlineStr">
         <is>
+          <t>我係辦公室行政助理麥峻容，根據曹總經理指示，煩請 閣下協助處理其病假期間嘅工作。</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>煩請 閣下協助處理其病假期間嘅工作。我係辦公室行政助理麥峻容，根據曹總經理指示，</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="inlineStr">
+        <is>
           <t>根據曹總經理指示，煩請 閣下協助處理其病假期間嘅工作。我係辦公室行政助理麥峻容，</t>
-        </is>
-      </c>
-      <c r="D15" s="25" t="inlineStr">
-        <is>
-          <t>煩請 閣下協助處理其病假期間嘅工作。我係辦公室行政助理麥峻容，根據曹總經理指示，</t>
-        </is>
-      </c>
-      <c r="E15" s="25" t="inlineStr">
-        <is>
-          <t>我係辦公室行政助理麥峻容，根據曹總經理指示，煩請 閣下協助處理其病假期間嘅工作。</t>
         </is>
       </c>
       <c r="F15" s="25" t="inlineStr"/>
@@ -957,7 +957,7 @@
       </c>
       <c r="H15" s="26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I15" s="1" t="n"/>
@@ -973,22 +973,22 @@
       </c>
       <c r="C16" s="25" t="inlineStr">
         <is>
+          <t>客人鍾意字多</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
           <t>有發送時間同記錄，可作書面憑證</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="E16" s="25" t="inlineStr">
+        <is>
+          <t>冇原因</t>
+        </is>
+      </c>
+      <c r="F16" s="25" t="inlineStr">
         <is>
           <t>電郵比較快</t>
-        </is>
-      </c>
-      <c r="E16" s="25" t="inlineStr">
-        <is>
-          <t>客人鍾意字多</t>
-        </is>
-      </c>
-      <c r="F16" s="25" t="inlineStr">
-        <is>
-          <t>冇原因</t>
         </is>
       </c>
       <c r="G16" s="25" t="n">
@@ -996,7 +996,7 @@
       </c>
       <c r="H16" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I16" s="1" t="n"/>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C17" s="25" t="inlineStr">
         <is>
+          <t>標題要簡明扼要</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
           <t>只需知悉唔使執行</t>
-        </is>
-      </c>
-      <c r="D17" s="25" t="inlineStr">
-        <is>
-          <t>標題要簡明扼要</t>
         </is>
       </c>
       <c r="E17" s="25" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="H17" s="26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I17" s="1" t="n"/>
@@ -1051,22 +1051,22 @@
       </c>
       <c r="C18" s="25" t="inlineStr">
         <is>
+          <t>顏色靚啲</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>冇附單</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="inlineStr">
+        <is>
+          <t>遲咗七日</t>
+        </is>
+      </c>
+      <c r="F18" s="25" t="inlineStr">
+        <is>
           <t>裝訂機完全冇送到，亦冇預先通知</t>
-        </is>
-      </c>
-      <c r="D18" s="25" t="inlineStr">
-        <is>
-          <t>遲咗七日</t>
-        </is>
-      </c>
-      <c r="E18" s="25" t="inlineStr">
-        <is>
-          <t>顏色靚啲</t>
-        </is>
-      </c>
-      <c r="F18" s="25" t="inlineStr">
-        <is>
-          <t>冇附單</t>
         </is>
       </c>
       <c r="G18" s="25" t="n">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="H18" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I18" s="1" t="n"/>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="C19" s="25" t="inlineStr">
         <is>
+          <t>醒</t>
+        </is>
+      </c>
+      <c r="D19" s="25" t="inlineStr">
+        <is>
           <t>反</t>
-        </is>
-      </c>
-      <c r="D19" s="25" t="inlineStr">
-        <is>
-          <t>醒</t>
         </is>
       </c>
       <c r="E19" s="25" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="H19" s="26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I19" s="1" t="n"/>
@@ -1121,22 +1121,22 @@
       </c>
       <c r="C20" s="25" t="inlineStr">
         <is>
+          <t>唔好意思</t>
+        </is>
+      </c>
+      <c r="D20" s="25" t="inlineStr">
+        <is>
           <t>抱歉</t>
         </is>
       </c>
-      <c r="D20" s="25" t="inlineStr">
-        <is>
-          <t>唔好意思</t>
-        </is>
-      </c>
       <c r="E20" s="25" t="inlineStr">
         <is>
+          <t>對唔住喇</t>
+        </is>
+      </c>
+      <c r="F20" s="25" t="inlineStr">
+        <is>
           <t>sorry</t>
-        </is>
-      </c>
-      <c r="F20" s="25" t="inlineStr">
-        <is>
-          <t>對唔住喇</t>
         </is>
       </c>
       <c r="G20" s="25" t="n">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H20" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I20" s="1" t="n"/>
@@ -1234,22 +1234,22 @@
       </c>
       <c r="C23" s="25" t="inlineStr">
         <is>
+          <t>IG private message</t>
+        </is>
+      </c>
+      <c r="D23" s="25" t="inlineStr">
+        <is>
+          <t>口頭估價</t>
+        </is>
+      </c>
+      <c r="E23" s="25" t="inlineStr">
+        <is>
+          <t>喺健身室口講</t>
+        </is>
+      </c>
+      <c r="F23" s="25" t="inlineStr">
+        <is>
           <t>電郵列明報價單附件</t>
-        </is>
-      </c>
-      <c r="D23" s="25" t="inlineStr">
-        <is>
-          <t>口頭估價</t>
-        </is>
-      </c>
-      <c r="E23" s="25" t="inlineStr">
-        <is>
-          <t>IG private message</t>
-        </is>
-      </c>
-      <c r="F23" s="25" t="inlineStr">
-        <is>
-          <t>喺健身室口講</t>
         </is>
       </c>
       <c r="G23" s="25" t="n">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="H23" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I23" s="1" t="n"/>
@@ -1278,17 +1278,17 @@
       </c>
       <c r="D24" s="25" t="inlineStr">
         <is>
+          <t>標題要簡明扼要</t>
+        </is>
+      </c>
+      <c r="E24" s="25" t="inlineStr">
+        <is>
+          <t>受文者電郵地址</t>
+        </is>
+      </c>
+      <c r="F24" s="25" t="inlineStr">
+        <is>
           <t>暗中通知嘅受文人</t>
-        </is>
-      </c>
-      <c r="E24" s="25" t="inlineStr">
-        <is>
-          <t>標題要簡明扼要</t>
-        </is>
-      </c>
-      <c r="F24" s="25" t="inlineStr">
-        <is>
-          <t>受文者電郵地址</t>
         </is>
       </c>
       <c r="G24" s="25" t="n">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="D25" s="25" t="inlineStr">
         <is>
+          <t>13日</t>
+        </is>
+      </c>
+      <c r="E25" s="25" t="inlineStr">
+        <is>
           <t>5日</t>
-        </is>
-      </c>
-      <c r="E25" s="25" t="inlineStr">
-        <is>
-          <t>13日</t>
         </is>
       </c>
       <c r="F25" s="25" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C26" s="25" t="inlineStr">
         <is>
+          <t>議</t>
+        </is>
+      </c>
+      <c r="D26" s="25" t="inlineStr">
+        <is>
           <t>相</t>
-        </is>
-      </c>
-      <c r="D26" s="25" t="inlineStr">
-        <is>
-          <t>議</t>
         </is>
       </c>
       <c r="E26" s="25" t="inlineStr"/>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H26" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I26" s="1" t="n"/>
@@ -1387,17 +1387,17 @@
       </c>
       <c r="D27" s="25" t="inlineStr">
         <is>
+          <t>throw畀你</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="inlineStr">
+        <is>
+          <t>send咗</t>
+        </is>
+      </c>
+      <c r="F27" s="25" t="inlineStr">
+        <is>
           <t>俾埋</t>
-        </is>
-      </c>
-      <c r="E27" s="25" t="inlineStr">
-        <is>
-          <t>send咗</t>
-        </is>
-      </c>
-      <c r="F27" s="25" t="inlineStr">
-        <is>
-          <t>throw畀你</t>
         </is>
       </c>
       <c r="G27" s="25" t="n">
@@ -1421,22 +1421,22 @@
       </c>
       <c r="C28" s="25" t="inlineStr">
         <is>
+          <t>開例會</t>
+        </is>
+      </c>
+      <c r="D28" s="25" t="inlineStr">
+        <is>
           <t>要拜訪客戶</t>
         </is>
       </c>
-      <c r="D28" s="25" t="inlineStr">
+      <c r="E28" s="25" t="inlineStr">
+        <is>
+          <t>去廣州</t>
+        </is>
+      </c>
+      <c r="F28" s="25" t="inlineStr">
         <is>
           <t>身體檢查</t>
-        </is>
-      </c>
-      <c r="E28" s="25" t="inlineStr">
-        <is>
-          <t>開例會</t>
-        </is>
-      </c>
-      <c r="F28" s="25" t="inlineStr">
-        <is>
-          <t>去廣州</t>
         </is>
       </c>
       <c r="G28" s="25" t="n">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="H28" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I28" s="1" t="n"/>
@@ -1460,17 +1460,17 @@
       </c>
       <c r="C29" s="27" t="inlineStr">
         <is>
+          <t>煩請致電2852 4781與本人聯絡。謝謝！如有任何問題，</t>
+        </is>
+      </c>
+      <c r="D29" s="27" t="inlineStr">
+        <is>
           <t>如有任何問題，煩請致電2852 4781與本人聯絡。謝謝！</t>
         </is>
       </c>
-      <c r="D29" s="27" t="inlineStr">
+      <c r="E29" s="27" t="inlineStr">
         <is>
           <t>與本人聯絡。謝謝！如有任何問題，煩請致電2852 4781</t>
-        </is>
-      </c>
-      <c r="E29" s="27" t="inlineStr">
-        <is>
-          <t>煩請致電2852 4781與本人聯絡。謝謝！如有任何問題，</t>
         </is>
       </c>
       <c r="F29" s="27" t="inlineStr"/>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="H29" s="28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I29" s="1" t="n"/>
